--- a/backend/results/analytics_results.xlsx
+++ b/backend/results/analytics_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q8"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1031,13 +1031,246 @@
           <t>neutral</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>25</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>temp_1788185463384_sample_call_2.wav</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-09-04T12:23:19.333722Z</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>The call was focused on confirming required documents for a loan application.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>temp_1788524590494_sample_call_2.wav</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-09-04T12:24:29.571039Z</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Not Provided</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>The call was between an agent named Pam from Windows and a customer inquiring about window-based marketing services. The agent explained their interactive display solution and attempted to schedule a demonstration with the company's VP. The customer seemed cooperative but mostly focused on setting up an appointment to understand the cost aspect.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Schedule demonstration with VP</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>temp_1788524646684_videoplayback (4) (1) - Copy.mp3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-09-04T16:18:27.978503Z</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Not provided</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>English</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cold</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>25</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>The call was a follow-up between an agent and a customer to discuss setting up a meeting to go over an online platform. No specific property requirements or real estate interests were identified.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>temp_1788538680637_videoplayback (25).m4a</t>
         </is>
       </c>
     </row>
